--- a/Demande.xlsx
+++ b/Demande.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\torrs\Documents\GitHub\Dossier-Projet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A88DE19-DEA5-45CE-9652-92B4700CA283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F230017-34AE-4559-AFFF-D324E578A3D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F2C3C7CA-1020-445D-8B0F-B248B60A8358}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="84">
   <si>
     <t>PRO BTP groupe</t>
   </si>
@@ -240,13 +240,61 @@
   </si>
   <si>
     <t>contact-paca@arcesi-ea.com</t>
+  </si>
+  <si>
+    <t>Doxallia</t>
+  </si>
+  <si>
+    <t>drh.formation@doxallia.com</t>
+  </si>
+  <si>
+    <t>Vinci</t>
+  </si>
+  <si>
+    <t>Développeur Full Stack</t>
+  </si>
+  <si>
+    <t>itekway</t>
+  </si>
+  <si>
+    <t>site</t>
+  </si>
+  <si>
+    <t>apside</t>
+  </si>
+  <si>
+    <t>techvalley</t>
+  </si>
+  <si>
+    <t>contact@techvalley.fr</t>
+  </si>
+  <si>
+    <t>job in live</t>
+  </si>
+  <si>
+    <t>aktisea</t>
+  </si>
+  <si>
+    <t>sendoc</t>
+  </si>
+  <si>
+    <t>DARWINI</t>
+  </si>
+  <si>
+    <t>Offre</t>
+  </si>
+  <si>
+    <t>Koesio</t>
+  </si>
+  <si>
+    <t>Hepic</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -328,16 +376,41 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="17"/>
+      <color rgb="FF1A202C"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -345,11 +418,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -373,6 +461,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -707,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B301771B-73D6-446E-9AAD-3D45609E0EF8}">
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -1311,6 +1409,160 @@
         <v>45568</v>
       </c>
     </row>
+    <row r="41" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="C41" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="2">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>70</v>
+      </c>
+      <c r="B42" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D42" s="2">
+        <v>45581</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>72</v>
+      </c>
+      <c r="B43" t="s">
+        <v>73</v>
+      </c>
+      <c r="C43" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43" s="2">
+        <v>45583</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>74</v>
+      </c>
+      <c r="B44" t="s">
+        <v>73</v>
+      </c>
+      <c r="C44" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" s="2">
+        <v>45583</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>75</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C45" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" s="2">
+        <v>45583</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>77</v>
+      </c>
+      <c r="B46" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" s="2">
+        <v>45583</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>78</v>
+      </c>
+      <c r="B47" t="s">
+        <v>73</v>
+      </c>
+      <c r="C47" t="s">
+        <v>7</v>
+      </c>
+      <c r="D47" s="2">
+        <v>45583</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>79</v>
+      </c>
+      <c r="B48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" s="2">
+        <v>45583</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="21.75" x14ac:dyDescent="0.25">
+      <c r="A49" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="B49" t="s">
+        <v>56</v>
+      </c>
+      <c r="C49" t="s">
+        <v>81</v>
+      </c>
+      <c r="D49" s="2">
+        <v>45596</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>82</v>
+      </c>
+      <c r="B50" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" s="2">
+        <v>45600</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>83</v>
+      </c>
+      <c r="B51" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" t="s">
+        <v>7</v>
+      </c>
+      <c r="D51" s="2">
+        <v>45601</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/Demande.xlsx
+++ b/Demande.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\torrs\Documents\GitHub\Dossier-Projet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885E53BE-5608-4C3A-9267-0E8EF32C1DF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED275739-03D2-496C-8648-0FE2E17B2118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F2C3C7CA-1020-445D-8B0F-B248B60A8358}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="67">
   <si>
     <t>ENTREPRISE</t>
   </si>
@@ -135,13 +135,115 @@
   </si>
   <si>
     <t>carole.maguet@dgfip.finances.gouv.fr</t>
+  </si>
+  <si>
+    <t>Mission handicap</t>
+  </si>
+  <si>
+    <t>Depot de CV et inscription</t>
+  </si>
+  <si>
+    <t>Inscription</t>
+  </si>
+  <si>
+    <t>iTekway</t>
+  </si>
+  <si>
+    <t>human connexion</t>
+  </si>
+  <si>
+    <t>site</t>
+  </si>
+  <si>
+    <t>Crypteo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	contact@crypteo.com</t>
+  </si>
+  <si>
+    <t>Développeur fullstack/apprenti ingénieur en informatique (sncf)</t>
+  </si>
+  <si>
+    <t>Offre</t>
+  </si>
+  <si>
+    <t>INTÉGRATEUR / OPS - DÉPLOIEMENT APPLICATIF (SNCF)</t>
+  </si>
+  <si>
+    <t>refus 05/05/2025</t>
+  </si>
+  <si>
+    <t>Xegen</t>
+  </si>
+  <si>
+    <t>contact@xegen.fr</t>
+  </si>
+  <si>
+    <t>Sacha</t>
+  </si>
+  <si>
+    <t>contact@experhygia.com</t>
+  </si>
+  <si>
+    <t>refus 06/05/2025</t>
+  </si>
+  <si>
+    <t>Airbus Apprenti(e) Data Analyst</t>
+  </si>
+  <si>
+    <t>offre</t>
+  </si>
+  <si>
+    <t>Airbus Apprenti(e) Ingénieur(e) en Analyse de Données</t>
+  </si>
+  <si>
+    <t>refus (offre close…) 06/05/2025</t>
+  </si>
+  <si>
+    <t>Jalis</t>
+  </si>
+  <si>
+    <t>Pole Emploi</t>
+  </si>
+  <si>
+    <t>La boite immo</t>
+  </si>
+  <si>
+    <t>Guarani Mediterannée</t>
+  </si>
+  <si>
+    <t>CityWay</t>
+  </si>
+  <si>
+    <t>High co data</t>
+  </si>
+  <si>
+    <t>Eukles solution</t>
+  </si>
+  <si>
+    <t>Silae</t>
+  </si>
+  <si>
+    <t>Echoes</t>
+  </si>
+  <si>
+    <t>Novrh</t>
+  </si>
+  <si>
+    <t>h 2022</t>
+  </si>
+  <si>
+    <t>amiltone</t>
+  </si>
+  <si>
+    <t>ALPHA10X</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -272,6 +374,25 @@
     <font>
       <sz val="17"/>
       <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF6558B1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F0335"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -318,7 +439,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -378,6 +499,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -810,6 +940,9 @@
       <c r="D6" s="2">
         <v>45780</v>
       </c>
+      <c r="E6" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="7" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="21" t="s">
@@ -824,12 +957,15 @@
       <c r="D7" s="2">
         <v>45780</v>
       </c>
+      <c r="E7" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="8" spans="1:5" ht="30.75" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="16" t="s">
         <v>20</v>
       </c>
       <c r="C8" t="s">
@@ -837,6 +973,9 @@
       </c>
       <c r="D8" s="2">
         <v>45780</v>
+      </c>
+      <c r="E8" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="83.25" x14ac:dyDescent="0.25">
@@ -880,6 +1019,9 @@
       <c r="D11" s="2">
         <v>45780</v>
       </c>
+      <c r="E11" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="12" spans="1:5" ht="43.5" x14ac:dyDescent="0.3">
       <c r="A12" s="25" t="s">
@@ -923,83 +1065,334 @@
         <v>45780</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C15" s="6"/>
-      <c r="D15" s="2"/>
+    <row r="15" spans="1:5" ht="21.75" x14ac:dyDescent="0.3">
+      <c r="A15" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="2">
+        <v>45780</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C16" s="6"/>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D17" s="2"/>
+      <c r="A16" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="2">
+        <v>45780</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="21.75" x14ac:dyDescent="0.3">
+      <c r="A17" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="2">
+        <v>45780</v>
+      </c>
       <c r="G17" s="7"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D23" s="2"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D25" s="2"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D26" s="2"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D27" s="2"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D28" s="2"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D29" s="2"/>
+    <row r="18" spans="1:7" ht="21.75" x14ac:dyDescent="0.3">
+      <c r="A18" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="2">
+        <v>45780</v>
+      </c>
+      <c r="E18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="2">
+        <v>45782</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="116.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="2">
+        <v>45782</v>
+      </c>
+      <c r="E20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="21.75" x14ac:dyDescent="0.3">
+      <c r="A21" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="2">
+        <v>45782</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="21.75" x14ac:dyDescent="0.3">
+      <c r="A22" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="2">
+        <v>45782</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="21.75" x14ac:dyDescent="0.3">
+      <c r="A23" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="2">
+        <v>45782</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="43.5" x14ac:dyDescent="0.3">
+      <c r="A24" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="2">
+        <v>45783</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="87" x14ac:dyDescent="0.3">
+      <c r="A25" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" s="2">
+        <v>45783</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="21.75" x14ac:dyDescent="0.3">
+      <c r="A26" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="2">
+        <v>45783</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="21.75" x14ac:dyDescent="0.3">
+      <c r="A27" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="2">
+        <v>45783</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="43.5" x14ac:dyDescent="0.3">
+      <c r="A28" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="2">
+        <v>45783</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="21.75" x14ac:dyDescent="0.3">
+      <c r="A29" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="2">
+        <v>45783</v>
+      </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="8"/>
-      <c r="B30" s="19"/>
-      <c r="D30" s="2"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D31" s="2"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D32" s="2"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D33" s="2"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D34" s="2"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C35" s="6"/>
-      <c r="D35" s="2"/>
+      <c r="A30" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="2">
+        <v>45783</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="21.75" x14ac:dyDescent="0.3">
+      <c r="A31" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C31" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="2">
+        <v>45783</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="21.75" x14ac:dyDescent="0.3">
+      <c r="A32" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="2">
+        <v>45783</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="21.75" x14ac:dyDescent="0.3">
+      <c r="A33" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C33" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="2">
+        <v>45783</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="21.75" x14ac:dyDescent="0.3">
+      <c r="A34" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C34" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="2">
+        <v>45783</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="21.75" x14ac:dyDescent="0.3">
+      <c r="A35" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="2">
+        <v>45783</v>
+      </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="11"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="2"/>
+      <c r="A36" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="2">
+        <v>45783</v>
+      </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C37" s="10"/>
-      <c r="D37" s="2"/>
+      <c r="A37" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="2">
+        <v>45783</v>
+      </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D38" s="2"/>
@@ -1053,8 +1446,10 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{B2D35FA5-DB98-4917-B209-C1982F16F35D}"/>
+    <hyperlink ref="B22" r:id="rId2" display="mailto:contact@experhygia.com" xr:uid="{0E84BB95-9D75-449B-BC4F-5F13F0DD6838}"/>
+    <hyperlink ref="B8" r:id="rId3" xr:uid="{854ED352-3EED-4348-8572-44D9FEF280F1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId4"/>
 </worksheet>
 </file>
--- a/Demande.xlsx
+++ b/Demande.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\torrs\Documents\GitHub\Dossier-Projet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED275739-03D2-496C-8648-0FE2E17B2118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0260D2E-0263-4D50-B796-0851B5AFFB55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F2C3C7CA-1020-445D-8B0F-B248B60A8358}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="68">
   <si>
     <t>ENTREPRISE</t>
   </si>
@@ -237,6 +237,9 @@
   </si>
   <si>
     <t>ALPHA10X</t>
+  </si>
+  <si>
+    <t>refus 15/05/2025</t>
   </si>
 </sst>
 </file>
@@ -1050,6 +1053,9 @@
       <c r="D13" s="2">
         <v>45780</v>
       </c>
+      <c r="E13" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="14" spans="1:5" ht="43.5" x14ac:dyDescent="0.3">
       <c r="A14" s="25" t="s">

--- a/Demande.xlsx
+++ b/Demande.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\torrs\Documents\GitHub\Dossier-Projet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0260D2E-0263-4D50-B796-0851B5AFFB55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C83831BE-B7D4-4E4C-A498-44AC0163D3D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F2C3C7CA-1020-445D-8B0F-B248B60A8358}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{F2C3C7CA-1020-445D-8B0F-B248B60A8358}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="70">
   <si>
     <t>ENTREPRISE</t>
   </si>
@@ -240,13 +240,19 @@
   </si>
   <si>
     <t>refus 15/05/2025</t>
+  </si>
+  <si>
+    <t>ALTO GROUP</t>
+  </si>
+  <si>
+    <t>https://occitanie.jobs/postuler_offre.php?idof=404408</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -396,6 +402,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF1F0335"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF96A2B2"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -442,7 +454,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -511,6 +523,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -847,16 +862,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B301771B-73D6-446E-9AAD-3D45609E0EF8}">
   <dimension ref="A1:G51"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" customWidth="1"/>
+    <col min="1" max="1" width="28.7265625" customWidth="1"/>
     <col min="2" max="2" width="31" style="18" customWidth="1"/>
     <col min="3" max="3" width="38" customWidth="1"/>
-    <col min="4" max="4" width="36.140625" customWidth="1"/>
-    <col min="5" max="5" width="41.140625" customWidth="1"/>
+    <col min="4" max="4" width="36.1796875" customWidth="1"/>
+    <col min="5" max="5" width="41.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="34.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:5" ht="34.5" x14ac:dyDescent="0.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -873,7 +888,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="58" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -887,7 +902,7 @@
         <v>45779</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -901,7 +916,7 @@
         <v>45779</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -916,7 +931,7 @@
       </c>
       <c r="E4" s="5"/>
     </row>
-    <row r="5" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="17" x14ac:dyDescent="0.35">
       <c r="A5" s="20" t="s">
         <v>12</v>
       </c>
@@ -930,7 +945,7 @@
         <v>45780</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="116" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -947,7 +962,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="21" t="s">
         <v>18</v>
       </c>
@@ -964,7 +979,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="30.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="31" x14ac:dyDescent="0.35">
       <c r="A8" s="21" t="s">
         <v>19</v>
       </c>
@@ -981,7 +996,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="83.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="84" x14ac:dyDescent="0.35">
       <c r="A9" s="23" t="s">
         <v>21</v>
       </c>
@@ -995,7 +1010,7 @@
         <v>45780</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="270" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="270" x14ac:dyDescent="0.35">
       <c r="A10" s="22" t="s">
         <v>23</v>
       </c>
@@ -1009,7 +1024,7 @@
         <v>45780</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="87" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="84" x14ac:dyDescent="0.4">
       <c r="A11" s="25" t="s">
         <v>26</v>
       </c>
@@ -1026,7 +1041,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="43.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="42" x14ac:dyDescent="0.4">
       <c r="A12" s="25" t="s">
         <v>27</v>
       </c>
@@ -1040,7 +1055,7 @@
         <v>45780</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="26" t="s">
         <v>29</v>
       </c>
@@ -1057,7 +1072,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="43.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="42" x14ac:dyDescent="0.4">
       <c r="A14" s="25" t="s">
         <v>31</v>
       </c>
@@ -1071,7 +1086,7 @@
         <v>45780</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="21.75" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="21" x14ac:dyDescent="0.4">
       <c r="A15" s="25" t="s">
         <v>33</v>
       </c>
@@ -1085,7 +1100,7 @@
         <v>45780</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="27" t="s">
         <v>36</v>
       </c>
@@ -1099,7 +1114,7 @@
         <v>45780</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="21.75" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="21" x14ac:dyDescent="0.4">
       <c r="A17" s="25" t="s">
         <v>37</v>
       </c>
@@ -1114,7 +1129,7 @@
       </c>
       <c r="G17" s="7"/>
     </row>
-    <row r="18" spans="1:7" ht="21.75" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="21" x14ac:dyDescent="0.4">
       <c r="A18" s="25" t="s">
         <v>39</v>
       </c>
@@ -1131,7 +1146,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="25" t="s">
         <v>41</v>
       </c>
@@ -1145,7 +1160,7 @@
         <v>45782</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="116.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" ht="116.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="28" t="s">
         <v>43</v>
       </c>
@@ -1162,7 +1177,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="21.75" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="21" x14ac:dyDescent="0.4">
       <c r="A21" s="25" t="s">
         <v>45</v>
       </c>
@@ -1176,7 +1191,7 @@
         <v>45782</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="21.75" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="21" x14ac:dyDescent="0.4">
       <c r="A22" s="25" t="s">
         <v>47</v>
       </c>
@@ -1190,7 +1205,7 @@
         <v>45782</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="21.75" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="21" x14ac:dyDescent="0.4">
       <c r="A23" s="25" t="s">
         <v>5</v>
       </c>
@@ -1204,7 +1219,7 @@
         <v>45782</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="43.5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="42" x14ac:dyDescent="0.4">
       <c r="A24" s="25" t="s">
         <v>50</v>
       </c>
@@ -1218,7 +1233,7 @@
         <v>45783</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="87" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="84" x14ac:dyDescent="0.4">
       <c r="A25" s="25" t="s">
         <v>52</v>
       </c>
@@ -1232,7 +1247,7 @@
         <v>45783</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="21.75" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="21" x14ac:dyDescent="0.4">
       <c r="A26" s="25" t="s">
         <v>54</v>
       </c>
@@ -1246,7 +1261,7 @@
         <v>45783</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="21.75" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="21" x14ac:dyDescent="0.4">
       <c r="A27" s="25" t="s">
         <v>56</v>
       </c>
@@ -1260,7 +1275,7 @@
         <v>45783</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="43.5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="42" x14ac:dyDescent="0.4">
       <c r="A28" s="25" t="s">
         <v>57</v>
       </c>
@@ -1274,7 +1289,7 @@
         <v>45783</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="21.75" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="21" x14ac:dyDescent="0.4">
       <c r="A29" s="25" t="s">
         <v>58</v>
       </c>
@@ -1288,7 +1303,7 @@
         <v>45783</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="8" t="s">
         <v>59</v>
       </c>
@@ -1302,7 +1317,7 @@
         <v>45783</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="21.75" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="21" x14ac:dyDescent="0.4">
       <c r="A31" s="25" t="s">
         <v>60</v>
       </c>
@@ -1316,7 +1331,7 @@
         <v>45783</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="21.75" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="21" x14ac:dyDescent="0.4">
       <c r="A32" s="25" t="s">
         <v>61</v>
       </c>
@@ -1330,7 +1345,7 @@
         <v>45783</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="21.75" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" ht="21" x14ac:dyDescent="0.4">
       <c r="A33" s="25" t="s">
         <v>62</v>
       </c>
@@ -1344,7 +1359,7 @@
         <v>45783</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="21.75" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" ht="21" x14ac:dyDescent="0.4">
       <c r="A34" s="25" t="s">
         <v>63</v>
       </c>
@@ -1358,7 +1373,7 @@
         <v>45783</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="21.75" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" ht="21" x14ac:dyDescent="0.4">
       <c r="A35" s="25" t="s">
         <v>64</v>
       </c>
@@ -1372,7 +1387,7 @@
         <v>45783</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="11" t="s">
         <v>65</v>
       </c>
@@ -1386,7 +1401,7 @@
         <v>45783</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="31" t="s">
         <v>66</v>
       </c>
@@ -1400,53 +1415,64 @@
         <v>45783</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D38" s="2"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A38" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C38" t="s">
+        <v>42</v>
+      </c>
+      <c r="D38" s="2">
+        <v>45796</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D39" s="2"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B40" s="19"/>
       <c r="D40" s="2"/>
     </row>
-    <row r="41" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="12"/>
       <c r="B41" s="13"/>
       <c r="D41" s="2"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B42" s="14"/>
       <c r="C42" s="14"/>
       <c r="D42" s="2"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D43" s="2"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B45" s="19"/>
       <c r="D45" s="2"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D47" s="2"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" ht="21.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="21.5" x14ac:dyDescent="0.35">
       <c r="A49" s="15"/>
       <c r="D49" s="2"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D51" s="2"/>
     </row>
   </sheetData>

--- a/Demande.xlsx
+++ b/Demande.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\torrs\Documents\GitHub\Dossier-Projet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C83831BE-B7D4-4E4C-A498-44AC0163D3D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2184E0B-6326-4C34-AF00-DB3A6100AAC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{F2C3C7CA-1020-445D-8B0F-B248B60A8358}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="71">
   <si>
     <t>ENTREPRISE</t>
   </si>
@@ -246,6 +246,9 @@
   </si>
   <si>
     <t>https://occitanie.jobs/postuler_offre.php?idof=404408</t>
+  </si>
+  <si>
+    <t>refus 20/05/2025</t>
   </si>
 </sst>
 </file>
@@ -1345,7 +1348,7 @@
         <v>45783</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="21" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:5" ht="21" x14ac:dyDescent="0.4">
       <c r="A33" s="25" t="s">
         <v>62</v>
       </c>
@@ -1359,7 +1362,7 @@
         <v>45783</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="21" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:5" ht="21" x14ac:dyDescent="0.4">
       <c r="A34" s="25" t="s">
         <v>63</v>
       </c>
@@ -1373,7 +1376,7 @@
         <v>45783</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="21" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:5" ht="21" x14ac:dyDescent="0.4">
       <c r="A35" s="25" t="s">
         <v>64</v>
       </c>
@@ -1387,7 +1390,7 @@
         <v>45783</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="11" t="s">
         <v>65</v>
       </c>
@@ -1401,7 +1404,7 @@
         <v>45783</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="31" t="s">
         <v>66</v>
       </c>
@@ -1415,7 +1418,7 @@
         <v>45783</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A38" s="32" t="s">
         <v>68</v>
       </c>
@@ -1428,41 +1431,44 @@
       <c r="D38" s="2">
         <v>45796</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E38" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D39" s="2"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B40" s="19"/>
       <c r="D40" s="2"/>
     </row>
-    <row r="41" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="12"/>
       <c r="B41" s="13"/>
       <c r="D41" s="2"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B42" s="14"/>
       <c r="C42" s="14"/>
       <c r="D42" s="2"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D43" s="2"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B45" s="19"/>
       <c r="D45" s="2"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D47" s="2"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D48" s="2"/>
     </row>
     <row r="49" spans="1:4" ht="21.5" x14ac:dyDescent="0.35">

--- a/Demande.xlsx
+++ b/Demande.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\torrs\Documents\GitHub\Dossier-Projet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2184E0B-6326-4C34-AF00-DB3A6100AAC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{648E83BC-B866-48BE-8D1B-B4BB14BA5F57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{F2C3C7CA-1020-445D-8B0F-B248B60A8358}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="82">
   <si>
     <t>ENTREPRISE</t>
   </si>
@@ -249,13 +249,46 @@
   </si>
   <si>
     <t>refus 20/05/2025</t>
+  </si>
+  <si>
+    <t>Naval groupe</t>
+  </si>
+  <si>
+    <t>Alternant - Concepteur logiciel embarqué</t>
+  </si>
+  <si>
+    <t>AGEFIPH</t>
+  </si>
+  <si>
+    <t>Ingénieur Devops</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>INDEED</t>
+  </si>
+  <si>
+    <t>Concepteur Développeur en alternance</t>
+  </si>
+  <si>
+    <t>REFUS 22/05/2025</t>
+  </si>
+  <si>
+    <t>sogeti</t>
+  </si>
+  <si>
+    <t>indeed</t>
+  </si>
+  <si>
+    <t>Alternance en Développement web FullStack</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -411,6 +444,25 @@
     <font>
       <sz val="9"/>
       <color rgb="FF96A2B2"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13.5"/>
+      <color rgb="FF061835"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color rgb="FF2D2D2D"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -457,7 +509,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -527,6 +579,13 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -869,7 +928,7 @@
   <cols>
     <col min="1" max="1" width="28.7265625" customWidth="1"/>
     <col min="2" max="2" width="31" style="18" customWidth="1"/>
-    <col min="3" max="3" width="38" customWidth="1"/>
+    <col min="3" max="3" width="40.81640625" customWidth="1"/>
     <col min="4" max="4" width="36.1796875" customWidth="1"/>
     <col min="5" max="5" width="41.1796875" customWidth="1"/>
   </cols>
@@ -1435,22 +1494,64 @@
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="D39" s="2"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B40" s="19"/>
-      <c r="D40" s="2"/>
+    <row r="39" spans="1:5" ht="34" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>71</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="D39" s="2">
+        <v>45798</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="17" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>71</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C40" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="D40" s="2">
+        <v>45798</v>
+      </c>
     </row>
     <row r="41" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A41" s="12"/>
-      <c r="B41" s="13"/>
-      <c r="D41" s="2"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="2"/>
+      <c r="A41" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C41" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="D41" s="2">
+        <v>45798</v>
+      </c>
+      <c r="E41" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="90" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>79</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C42" s="35" t="s">
+        <v>81</v>
+      </c>
+      <c r="D42" s="2">
+        <v>45800</v>
+      </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D43" s="2"/>
